--- a/accor/data/model_data.xlsx
+++ b/accor/data/model_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="model_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,1128 +413,1133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HP127"/>
+  <dimension ref="A1:HQ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>hotel_code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hotel_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nom_hotel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>hotel_brand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>logo_path</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>hotel_adresse_postale_1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>hotel_adresse_postale_2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>hotel_code_postal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>hotel_city</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>hotel_lat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hotel_lon</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>annee</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>mois</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>departement</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>commune</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>nombre_categories_mois_f_b</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>nombre_categories_mois_n_f_b</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>pct_categories_mois_f_b</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>pct_categories_mois_n_f_b</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pct_cat_f_b_nombre_ventes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pct_cat_n_f_b_nombre_ventes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pct_sous_cat_accessoires_nombre_ventes</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pct_sous_cat_alcool_nombre_ventes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pct_sous_cat_cosmetique_nombre_ventes</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_salee_nombre_ventes</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_sucree_nombre_ventes</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pct_sous_cat_jeux_enfants_nombre_ventes</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pct_sous_cat_pap_nombre_ventes</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sans_alcool_nombre_ventes</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sos_nombre_ventes</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pct_sous_cat_souvenirs_nombre_ventes</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>zone_scolaire_a</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>zone_scolaire_b</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>zone_scolaire_c</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>nb_jours_dans_mois</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>nb_jours_feries</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>nb_jours_weekend</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>nb_jours_vacances_scolaires</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>nb_jours_vacances_hors_feries</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>nb_jours_holidays</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>pct_jours_holidays</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>weather_ok</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>weather_error</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>shard_id</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>meteo_temperature_c_mean</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>meteo_temperature_c_min</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>meteo_temperature_c_max</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>meteo_humidite_pct_mean</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>meteo_humidite_pct_min</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>meteo_humidite_pct_max</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>meteo_precipitations_mm_mean</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>meteo_precipitations_mm_min</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>meteo_precipitations_mm_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>meteo_vent_kmh_mean</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>meteo_vent_kmh_min</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>meteo_vent_kmh_max</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>meteo_pression_hpa_mean</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>meteo_pression_hpa_min</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>meteo_pression_hpa_max</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>meteo_ensoleillement_min_mean</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>meteo_ensoleillement_min_min</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>meteo_ensoleillement_min_max</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>commerce_convenience_100m</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>commerce_bakery_100m</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>commerce_cosmetics_100m</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>commerce_gift_100m</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>commerce_fb_100m</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>commerce_non_fb_100m</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>commerce_convenience_200m</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>commerce_bakery_200m</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>commerce_supermarket_200m</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>commerce_grocery_200m</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>commerce_cosmetics_200m</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>commerce_gift_200m</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>commerce_kiosk_200m</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>commerce_fb_200m</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>commerce_non_fb_200m</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>commerce_convenience_300m</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>commerce_bakery_300m</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>commerce_supermarket_300m</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>commerce_alcohol_300m</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>commerce_grocery_300m</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>commerce_cosmetics_300m</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>commerce_gift_300m</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>commerce_tobacco_300m</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>commerce_kiosk_300m</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>commerce_fb_300m</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>commerce_non_fb_300m</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>commerce_convenience_400m</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>commerce_bakery_400m</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>commerce_supermarket_400m</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>commerce_alcohol_400m</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>commerce_grocery_400m</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>commerce_cosmetics_400m</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>commerce_gift_400m</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>commerce_tobacco_400m</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>commerce_kiosk_400m</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>commerce_fb_400m</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>commerce_non_fb_400m</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>commerce_convenience_500m</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>commerce_bakery_500m</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>commerce_supermarket_500m</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>commerce_alcohol_500m</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>commerce_confectionery_500m</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>commerce_grocery_500m</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>commerce_cosmetics_500m</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>commerce_gift_500m</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>commerce_tobacco_500m</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>commerce_kiosk_500m</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>commerce_fb_500m</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>commerce_non_fb_500m</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>plage_1km</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>plage_2km</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>plage_3km</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>plage_4km</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>plage_5km</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>plage_distance_km</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>hotel_country</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>proximity_ok</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>hotel_contrat_signe_annee</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>hotel_derniere_reno</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>hotel_lobby_derniere_reno</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>hotel_nb_chambres</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>hotel_to_annuel</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>hotel_to_le_plus_bas_taux</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>hotel_to_le_plus_haut_taux</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_fontaine_a_eau</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_machine_a_cafe</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_micro_ondes</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_vitrine_refrigeree</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>hotel_f_b_bar</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>hotel_f_b_minibar</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>hotel_f_b_restaurant</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>hotel_f_b_room_service</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_piscine</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_salle_de_sport</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_salles_de_reunion</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>hotel_has_parking</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>hotel_has_animaux</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>hotel_has_reunion</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>hotel_affaires_pct</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>hotel_loisirs_pct</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_amis</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_couples</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_familles</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>hotel_international_pct</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>hotel_national_pct</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_existe_deja</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>hotel_corner_de_vente_actuel_metres_lineaires</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_distributeur_auto</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_reception</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_snacking_comptoir</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_distributeur_auto</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_reception</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>hotel_metres_lineaires_dedies_corner</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>hotel_contrat_type_franchise</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>hotel_contrat_type_manage</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>cat_economy</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>cat_midscale</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>Nb_Hotels</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>Nb_Ch_0_49</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>Nb_Ch_50_99</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>Nb_Ch_100_149</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>Nb_Ch_150_199</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>Nb_Ch_200_249</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>Nb_Ch_250_299</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>Nb_Ch_300_Plus</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>Nb_Resto_0</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>Nb_Resto_1</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>Nb_Resto_2</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>Nb_Resto_3</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>Nb_Bar_0</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>Nb_Bar_1</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>Nb_Bar_2</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>Nb_Bar_3</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>nombre_ventes</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>montant_ventes</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>nombre_paniers</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>nombre_produits</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>pct_cat_f_b_montant_ventes</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>pct_cat_n_f_b_montant_ventes</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>pct_cat_f_b_nombre_paniers</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>pct_cat_n_f_b_nombre_paniers</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>pct_cat_f_b_nombre_produits</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>pct_cat_n_f_b_nombre_produits</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>pct_sous_cat_accessoires_montant_ventes</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>pct_sous_cat_alcool_montant_ventes</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>pct_sous_cat_cosmetique_montant_ventes</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_salee_montant_ventes</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_sucree_montant_ventes</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>pct_sous_cat_jeux_enfants_montant_ventes</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>pct_sous_cat_pap_montant_ventes</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sans_alcool_montant_ventes</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sos_montant_ventes</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>pct_sous_cat_souvenirs_montant_ventes</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>pct_sous_cat_accessoires_nombre_paniers</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>pct_sous_cat_alcool_nombre_paniers</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>pct_sous_cat_cosmetique_nombre_paniers</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_salee_nombre_paniers</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_sucree_nombre_paniers</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>pct_sous_cat_jeux_enfants_nombre_paniers</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>pct_sous_cat_pap_nombre_paniers</t>
         </is>
       </c>
-      <c r="GU1" s="1" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sans_alcool_nombre_paniers</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sos_nombre_paniers</t>
         </is>
       </c>
-      <c r="GW1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>pct_sous_cat_souvenirs_nombre_paniers</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>pct_sous_cat_accessoires_nombre_produits</t>
         </is>
       </c>
-      <c r="GY1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>pct_sous_cat_alcool_nombre_produits</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>pct_sous_cat_cosmetique_nombre_produits</t>
         </is>
       </c>
-      <c r="HA1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_salee_nombre_produits</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>pct_sous_cat_food_sucree_nombre_produits</t>
         </is>
       </c>
-      <c r="HC1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>pct_sous_cat_jeux_enfants_nombre_produits</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>pct_sous_cat_pap_nombre_produits</t>
         </is>
       </c>
-      <c r="HE1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sans_alcool_nombre_produits</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" t="inlineStr">
         <is>
           <t>pct_sous_cat_sos_nombre_produits</t>
         </is>
       </c>
-      <c r="HG1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>pct_sous_cat_souvenirs_nombre_produits</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>nombre_ventes_holidays</t>
         </is>
       </c>
-      <c r="HI1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
         <is>
           <t>montant_ventes_holidays</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>nombre_ventes_hors_holidays</t>
         </is>
       </c>
-      <c r="HK1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>montant_ventes_hors_holidays</t>
         </is>
       </c>
-      <c r="HL1" s="1" t="inlineStr">
+      <c r="HL1" t="inlineStr">
         <is>
           <t>pct_nombre_ventes_holidays</t>
         </is>
       </c>
-      <c r="HM1" s="1" t="inlineStr">
+      <c r="HM1" t="inlineStr">
         <is>
           <t>pct_montant_ventes_holidays</t>
         </is>
       </c>
-      <c r="HN1" s="1" t="inlineStr">
+      <c r="HN1" t="inlineStr">
         <is>
           <t>pct_nombre_ventes_hors_holidays</t>
         </is>
       </c>
-      <c r="HO1" s="1" t="inlineStr">
+      <c r="HO1" t="inlineStr">
         <is>
           <t>pct_montant_ventes_hors_holidays</t>
         </is>
       </c>
-      <c r="HP1" s="1" t="inlineStr">
+      <c r="HP1" t="inlineStr">
         <is>
           <t>_is_eval</t>
+        </is>
+      </c>
+      <c r="HQ1" t="inlineStr">
+        <is>
+          <t>brand_category</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1576,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1920,7 +1913,7 @@
       </c>
       <c r="DN2" t="inlineStr"/>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP2" t="n">
         <v>2020</v>
@@ -1935,13 +1928,13 @@
         <v>129</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU2" t="n">
         <v>0.6</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW2" t="n">
         <v>1</v>
@@ -1986,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL2" t="n">
         <v>0.6</v>
@@ -2001,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ2" t="n">
         <v>0.6</v>
@@ -2236,6 +2229,11 @@
       </c>
       <c r="HP2" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ2" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2271,7 +2269,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2608,7 +2606,7 @@
       </c>
       <c r="DN3" t="inlineStr"/>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
         <v>2020</v>
@@ -2623,13 +2621,13 @@
         <v>129</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU3" t="n">
         <v>0.6</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW3" t="n">
         <v>1</v>
@@ -2674,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL3" t="n">
         <v>0.6</v>
@@ -2689,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ3" t="n">
         <v>0.6</v>
@@ -2924,6 +2922,11 @@
       </c>
       <c r="HP3" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ3" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2959,7 +2962,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3296,7 +3299,7 @@
       </c>
       <c r="DN4" t="inlineStr"/>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP4" t="n">
         <v>2020</v>
@@ -3311,13 +3314,13 @@
         <v>129</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU4" t="n">
         <v>0.6</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW4" t="n">
         <v>1</v>
@@ -3362,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL4" t="n">
         <v>0.6</v>
@@ -3377,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ4" t="n">
         <v>0.6</v>
@@ -3612,6 +3615,11 @@
       </c>
       <c r="HP4" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ4" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3984,7 +3992,7 @@
       </c>
       <c r="DN5" t="inlineStr"/>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP5" t="n">
         <v>2020</v>
@@ -3999,13 +4007,13 @@
         <v>129</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU5" t="n">
         <v>0.6</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW5" t="n">
         <v>1</v>
@@ -4050,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL5" t="n">
         <v>0.6</v>
@@ -4065,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ5" t="n">
         <v>0.6</v>
@@ -4300,6 +4308,11 @@
       </c>
       <c r="HP5" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ5" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4335,7 +4348,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4672,10 +4685,10 @@
       </c>
       <c r="DN6" t="inlineStr"/>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP6" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ6" t="n">
         <v>2025</v>
@@ -4693,7 +4706,7 @@
         <v>0.6</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -4738,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL6" t="n">
         <v>0.6</v>
@@ -4753,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ6" t="n">
         <v>0.6</v>
@@ -4988,6 +5001,11 @@
       </c>
       <c r="HP6" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ6" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5023,7 +5041,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5360,10 +5378,10 @@
       </c>
       <c r="DN7" t="inlineStr"/>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP7" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ7" t="n">
         <v>2025</v>
@@ -5381,7 +5399,7 @@
         <v>0.6</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -5426,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL7" t="n">
         <v>0.6</v>
@@ -5441,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ7" t="n">
         <v>0.6</v>
@@ -5676,6 +5694,11 @@
       </c>
       <c r="HP7" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ7" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5711,7 +5734,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -6048,7 +6071,7 @@
       </c>
       <c r="DN8" t="inlineStr"/>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP8" t="n">
         <v>2020</v>
@@ -6063,13 +6086,13 @@
         <v>129</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU8" t="n">
         <v>0.6</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW8" t="n">
         <v>1</v>
@@ -6114,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL8" t="n">
         <v>0.6</v>
@@ -6129,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ8" t="n">
         <v>0.6</v>
@@ -6364,6 +6387,11 @@
       </c>
       <c r="HP8" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ8" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6399,7 +6427,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -6736,10 +6764,10 @@
       </c>
       <c r="DN9" t="inlineStr"/>
       <c r="DO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ9" t="n">
         <v>2025</v>
@@ -6757,7 +6785,7 @@
         <v>0.6</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
@@ -6802,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL9" t="n">
         <v>0.6</v>
@@ -6817,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ9" t="n">
         <v>0.6</v>
@@ -7052,6 +7080,11 @@
       </c>
       <c r="HP9" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ9" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7449,7 +7482,7 @@
         <v>0.6</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
@@ -7494,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL10" t="n">
         <v>0.6</v>
@@ -7509,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ10" t="n">
         <v>0.6</v>
@@ -7744,6 +7777,11 @@
       </c>
       <c r="HP10" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ10" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7779,7 +7817,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -8116,7 +8154,7 @@
       </c>
       <c r="DN11" t="inlineStr"/>
       <c r="DO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP11" t="n">
         <v>2020</v>
@@ -8131,13 +8169,13 @@
         <v>129</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU11" t="n">
         <v>0.6</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW11" t="n">
         <v>1</v>
@@ -8182,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL11" t="n">
         <v>0.6</v>
@@ -8197,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ11" t="n">
         <v>0.6</v>
@@ -8432,6 +8470,11 @@
       </c>
       <c r="HP11" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ11" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -8467,7 +8510,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -8804,10 +8847,10 @@
       </c>
       <c r="DN12" t="inlineStr"/>
       <c r="DO12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP12" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ12" t="n">
         <v>2025</v>
@@ -8825,7 +8868,7 @@
         <v>0.6</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
@@ -8870,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL12" t="n">
         <v>0.6</v>
@@ -8885,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ12" t="n">
         <v>0.6</v>
@@ -9120,6 +9163,11 @@
       </c>
       <c r="HP12" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ12" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -9517,7 +9565,7 @@
         <v>0.6</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
@@ -9562,7 +9610,7 @@
         <v>1</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL13" t="n">
         <v>0.6</v>
@@ -9577,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ13" t="n">
         <v>0.6</v>
@@ -9812,6 +9860,11 @@
       </c>
       <c r="HP13" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ13" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -9847,7 +9900,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -10184,7 +10237,7 @@
       </c>
       <c r="DN14" t="inlineStr"/>
       <c r="DO14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP14" t="n">
         <v>2020</v>
@@ -10199,13 +10252,13 @@
         <v>129</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU14" t="n">
         <v>0.6</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW14" t="n">
         <v>1</v>
@@ -10250,7 +10303,7 @@
         <v>1</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL14" t="n">
         <v>0.6</v>
@@ -10265,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ14" t="n">
         <v>0.6</v>
@@ -10500,6 +10553,11 @@
       </c>
       <c r="HP14" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ14" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10535,7 +10593,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -10872,10 +10930,10 @@
       </c>
       <c r="DN15" t="inlineStr"/>
       <c r="DO15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP15" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ15" t="n">
         <v>2025</v>
@@ -10893,7 +10951,7 @@
         <v>0.6</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
@@ -10938,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL15" t="n">
         <v>0.6</v>
@@ -10953,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ15" t="n">
         <v>0.6</v>
@@ -11188,6 +11246,11 @@
       </c>
       <c r="HP15" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ15" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -11223,7 +11286,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -11585,7 +11648,7 @@
         <v>0.6</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW16" t="n">
         <v>1</v>
@@ -11630,7 +11693,7 @@
         <v>1</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL16" t="n">
         <v>0.6</v>
@@ -11645,7 +11708,7 @@
         <v>1</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ16" t="n">
         <v>0.6</v>
@@ -11880,6 +11943,11 @@
       </c>
       <c r="HP16" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ16" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -12277,7 +12345,7 @@
         <v>0.6</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
@@ -12322,7 +12390,7 @@
         <v>1</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL17" t="n">
         <v>0.6</v>
@@ -12337,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ17" t="n">
         <v>0.6</v>
@@ -12572,6 +12640,11 @@
       </c>
       <c r="HP17" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ17" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -12607,7 +12680,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -12944,7 +13017,7 @@
       </c>
       <c r="DN18" t="inlineStr"/>
       <c r="DO18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP18" t="n">
         <v>2020</v>
@@ -12959,13 +13032,13 @@
         <v>129</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU18" t="n">
         <v>0.6</v>
       </c>
       <c r="DV18" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW18" t="n">
         <v>1</v>
@@ -13010,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL18" t="n">
         <v>0.6</v>
@@ -13025,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ18" t="n">
         <v>0.6</v>
@@ -13260,6 +13333,11 @@
       </c>
       <c r="HP18" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ18" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -13295,7 +13373,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -13632,10 +13710,10 @@
       </c>
       <c r="DN19" t="inlineStr"/>
       <c r="DO19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP19" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ19" t="n">
         <v>2025</v>
@@ -13653,7 +13731,7 @@
         <v>0.6</v>
       </c>
       <c r="DV19" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
@@ -13698,7 +13776,7 @@
         <v>1</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL19" t="n">
         <v>0.6</v>
@@ -13713,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ19" t="n">
         <v>0.6</v>
@@ -13948,6 +14026,11 @@
       </c>
       <c r="HP19" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ19" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -13983,7 +14066,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -14345,7 +14428,7 @@
         <v>0.6</v>
       </c>
       <c r="DV20" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW20" t="n">
         <v>1</v>
@@ -14390,7 +14473,7 @@
         <v>1</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL20" t="n">
         <v>0.6</v>
@@ -14405,7 +14488,7 @@
         <v>1</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ20" t="n">
         <v>0.6</v>
@@ -14640,6 +14723,11 @@
       </c>
       <c r="HP20" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ20" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -15037,7 +15125,7 @@
         <v>0.6</v>
       </c>
       <c r="DV21" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
@@ -15082,7 +15170,7 @@
         <v>1</v>
       </c>
       <c r="EK21" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL21" t="n">
         <v>0.6</v>
@@ -15097,7 +15185,7 @@
         <v>1</v>
       </c>
       <c r="EP21" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ21" t="n">
         <v>0.6</v>
@@ -15332,6 +15420,11 @@
       </c>
       <c r="HP21" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ21" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -15367,7 +15460,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -15704,7 +15797,7 @@
       </c>
       <c r="DN22" t="inlineStr"/>
       <c r="DO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP22" t="n">
         <v>2020</v>
@@ -15719,13 +15812,13 @@
         <v>129</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU22" t="n">
         <v>0.6</v>
       </c>
       <c r="DV22" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW22" t="n">
         <v>1</v>
@@ -15770,7 +15863,7 @@
         <v>1</v>
       </c>
       <c r="EK22" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL22" t="n">
         <v>0.6</v>
@@ -15785,7 +15878,7 @@
         <v>0</v>
       </c>
       <c r="EP22" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ22" t="n">
         <v>0.6</v>
@@ -16020,6 +16113,11 @@
       </c>
       <c r="HP22" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ22" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -16055,7 +16153,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -16392,10 +16490,10 @@
       </c>
       <c r="DN23" t="inlineStr"/>
       <c r="DO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP23" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ23" t="n">
         <v>2025</v>
@@ -16413,7 +16511,7 @@
         <v>0.6</v>
       </c>
       <c r="DV23" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW23" t="n">
         <v>0</v>
@@ -16458,7 +16556,7 @@
         <v>1</v>
       </c>
       <c r="EK23" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL23" t="n">
         <v>0.6</v>
@@ -16473,7 +16571,7 @@
         <v>0</v>
       </c>
       <c r="EP23" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ23" t="n">
         <v>0.6</v>
@@ -16708,6 +16806,11 @@
       </c>
       <c r="HP23" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ23" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -16743,7 +16846,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -17105,7 +17208,7 @@
         <v>0.6</v>
       </c>
       <c r="DV24" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW24" t="n">
         <v>1</v>
@@ -17150,7 +17253,7 @@
         <v>1</v>
       </c>
       <c r="EK24" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL24" t="n">
         <v>0.6</v>
@@ -17165,7 +17268,7 @@
         <v>1</v>
       </c>
       <c r="EP24" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ24" t="n">
         <v>0.6</v>
@@ -17400,6 +17503,11 @@
       </c>
       <c r="HP24" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ24" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -17797,7 +17905,7 @@
         <v>0.6</v>
       </c>
       <c r="DV25" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW25" t="n">
         <v>0</v>
@@ -17842,7 +17950,7 @@
         <v>1</v>
       </c>
       <c r="EK25" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL25" t="n">
         <v>0.6</v>
@@ -17857,7 +17965,7 @@
         <v>1</v>
       </c>
       <c r="EP25" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ25" t="n">
         <v>0.6</v>
@@ -18092,6 +18200,11 @@
       </c>
       <c r="HP25" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ25" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -18127,7 +18240,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -18464,7 +18577,7 @@
       </c>
       <c r="DN26" t="inlineStr"/>
       <c r="DO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP26" t="n">
         <v>2020</v>
@@ -18479,13 +18592,13 @@
         <v>129</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU26" t="n">
         <v>0.6</v>
       </c>
       <c r="DV26" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW26" t="n">
         <v>1</v>
@@ -18530,7 +18643,7 @@
         <v>1</v>
       </c>
       <c r="EK26" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL26" t="n">
         <v>0.6</v>
@@ -18545,7 +18658,7 @@
         <v>0</v>
       </c>
       <c r="EP26" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ26" t="n">
         <v>0.6</v>
@@ -18780,6 +18893,11 @@
       </c>
       <c r="HP26" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ26" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -18815,7 +18933,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -19152,10 +19270,10 @@
       </c>
       <c r="DN27" t="inlineStr"/>
       <c r="DO27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP27" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ27" t="n">
         <v>2025</v>
@@ -19173,7 +19291,7 @@
         <v>0.6</v>
       </c>
       <c r="DV27" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW27" t="n">
         <v>0</v>
@@ -19218,7 +19336,7 @@
         <v>1</v>
       </c>
       <c r="EK27" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL27" t="n">
         <v>0.6</v>
@@ -19233,7 +19351,7 @@
         <v>0</v>
       </c>
       <c r="EP27" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ27" t="n">
         <v>0.6</v>
@@ -19468,6 +19586,11 @@
       </c>
       <c r="HP27" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ27" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -19865,7 +19988,7 @@
         <v>0.6</v>
       </c>
       <c r="DV28" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW28" t="n">
         <v>0</v>
@@ -19910,7 +20033,7 @@
         <v>1</v>
       </c>
       <c r="EK28" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL28" t="n">
         <v>0.6</v>
@@ -19925,7 +20048,7 @@
         <v>1</v>
       </c>
       <c r="EP28" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ28" t="n">
         <v>0.6</v>
@@ -20160,6 +20283,11 @@
       </c>
       <c r="HP28" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ28" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -20195,7 +20323,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -20532,7 +20660,7 @@
       </c>
       <c r="DN29" t="inlineStr"/>
       <c r="DO29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP29" t="n">
         <v>2020</v>
@@ -20547,13 +20675,13 @@
         <v>129</v>
       </c>
       <c r="DT29" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU29" t="n">
         <v>0.6</v>
       </c>
       <c r="DV29" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW29" t="n">
         <v>1</v>
@@ -20598,7 +20726,7 @@
         <v>1</v>
       </c>
       <c r="EK29" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL29" t="n">
         <v>0.6</v>
@@ -20613,7 +20741,7 @@
         <v>0</v>
       </c>
       <c r="EP29" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ29" t="n">
         <v>0.6</v>
@@ -20848,6 +20976,11 @@
       </c>
       <c r="HP29" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ29" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -20883,7 +21016,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -21220,10 +21353,10 @@
       </c>
       <c r="DN30" t="inlineStr"/>
       <c r="DO30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP30" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ30" t="n">
         <v>2025</v>
@@ -21241,7 +21374,7 @@
         <v>0.6</v>
       </c>
       <c r="DV30" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW30" t="n">
         <v>0</v>
@@ -21286,7 +21419,7 @@
         <v>1</v>
       </c>
       <c r="EK30" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL30" t="n">
         <v>0.6</v>
@@ -21301,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="EP30" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ30" t="n">
         <v>0.6</v>
@@ -21536,6 +21669,11 @@
       </c>
       <c r="HP30" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ30" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -21571,7 +21709,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -21933,7 +22071,7 @@
         <v>0.6</v>
       </c>
       <c r="DV31" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW31" t="n">
         <v>1</v>
@@ -21978,7 +22116,7 @@
         <v>1</v>
       </c>
       <c r="EK31" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL31" t="n">
         <v>0.6</v>
@@ -21993,7 +22131,7 @@
         <v>1</v>
       </c>
       <c r="EP31" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ31" t="n">
         <v>0.6</v>
@@ -22228,6 +22366,11 @@
       </c>
       <c r="HP31" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ31" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -22625,7 +22768,7 @@
         <v>0.6</v>
       </c>
       <c r="DV32" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW32" t="n">
         <v>0</v>
@@ -22670,7 +22813,7 @@
         <v>1</v>
       </c>
       <c r="EK32" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL32" t="n">
         <v>0.6</v>
@@ -22685,7 +22828,7 @@
         <v>1</v>
       </c>
       <c r="EP32" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ32" t="n">
         <v>0.6</v>
@@ -22920,6 +23063,11 @@
       </c>
       <c r="HP32" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ32" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -22955,7 +23103,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -23292,7 +23440,7 @@
       </c>
       <c r="DN33" t="inlineStr"/>
       <c r="DO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP33" t="n">
         <v>2020</v>
@@ -23307,13 +23455,13 @@
         <v>129</v>
       </c>
       <c r="DT33" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU33" t="n">
         <v>0.6</v>
       </c>
       <c r="DV33" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW33" t="n">
         <v>1</v>
@@ -23358,7 +23506,7 @@
         <v>1</v>
       </c>
       <c r="EK33" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL33" t="n">
         <v>0.6</v>
@@ -23373,7 +23521,7 @@
         <v>0</v>
       </c>
       <c r="EP33" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ33" t="n">
         <v>0.6</v>
@@ -23608,6 +23756,11 @@
       </c>
       <c r="HP33" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ33" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -23643,7 +23796,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -23753,11 +23906,11 @@
         <v>0.548387</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
         <v>12.7</v>
@@ -24300,6 +24453,11 @@
       </c>
       <c r="HP34" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ34" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -24335,7 +24493,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -24672,10 +24830,10 @@
       </c>
       <c r="DN35" t="inlineStr"/>
       <c r="DO35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP35" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ35" t="n">
         <v>2025</v>
@@ -24693,7 +24851,7 @@
         <v>0.6</v>
       </c>
       <c r="DV35" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW35" t="n">
         <v>0</v>
@@ -24738,7 +24896,7 @@
         <v>1</v>
       </c>
       <c r="EK35" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL35" t="n">
         <v>0.6</v>
@@ -24753,7 +24911,7 @@
         <v>0</v>
       </c>
       <c r="EP35" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ35" t="n">
         <v>0.6</v>
@@ -24988,6 +25146,11 @@
       </c>
       <c r="HP35" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ35" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -25023,7 +25186,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -25385,7 +25548,7 @@
         <v>0.6</v>
       </c>
       <c r="DV36" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW36" t="n">
         <v>1</v>
@@ -25430,7 +25593,7 @@
         <v>1</v>
       </c>
       <c r="EK36" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL36" t="n">
         <v>0.6</v>
@@ -25445,7 +25608,7 @@
         <v>1</v>
       </c>
       <c r="EP36" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ36" t="n">
         <v>0.6</v>
@@ -25680,6 +25843,11 @@
       </c>
       <c r="HP36" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ36" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -26077,7 +26245,7 @@
         <v>0.6</v>
       </c>
       <c r="DV37" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW37" t="n">
         <v>0</v>
@@ -26122,7 +26290,7 @@
         <v>1</v>
       </c>
       <c r="EK37" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL37" t="n">
         <v>0.6</v>
@@ -26137,7 +26305,7 @@
         <v>1</v>
       </c>
       <c r="EP37" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ37" t="n">
         <v>0.6</v>
@@ -26372,6 +26540,11 @@
       </c>
       <c r="HP37" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ37" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -26407,7 +26580,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -26744,7 +26917,7 @@
       </c>
       <c r="DN38" t="inlineStr"/>
       <c r="DO38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP38" t="n">
         <v>2020</v>
@@ -26759,13 +26932,13 @@
         <v>129</v>
       </c>
       <c r="DT38" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU38" t="n">
         <v>0.6</v>
       </c>
       <c r="DV38" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW38" t="n">
         <v>1</v>
@@ -26810,7 +26983,7 @@
         <v>1</v>
       </c>
       <c r="EK38" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL38" t="n">
         <v>0.6</v>
@@ -26825,7 +26998,7 @@
         <v>0</v>
       </c>
       <c r="EP38" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ38" t="n">
         <v>0.6</v>
@@ -27060,6 +27233,11 @@
       </c>
       <c r="HP38" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ38" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -27095,7 +27273,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -27205,11 +27383,11 @@
         <v>0.366667</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
         <v>6.6</v>
@@ -27752,6 +27930,11 @@
       </c>
       <c r="HP39" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ39" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -27787,7 +27970,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -28124,10 +28307,10 @@
       </c>
       <c r="DN40" t="inlineStr"/>
       <c r="DO40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP40" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ40" t="n">
         <v>2025</v>
@@ -28145,7 +28328,7 @@
         <v>0.6</v>
       </c>
       <c r="DV40" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW40" t="n">
         <v>0</v>
@@ -28190,7 +28373,7 @@
         <v>1</v>
       </c>
       <c r="EK40" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL40" t="n">
         <v>0.6</v>
@@ -28205,7 +28388,7 @@
         <v>0</v>
       </c>
       <c r="EP40" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ40" t="n">
         <v>0.6</v>
@@ -28440,6 +28623,11 @@
       </c>
       <c r="HP40" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ40" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -28475,7 +28663,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -28837,7 +29025,7 @@
         <v>0.6</v>
       </c>
       <c r="DV41" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW41" t="n">
         <v>1</v>
@@ -28882,7 +29070,7 @@
         <v>1</v>
       </c>
       <c r="EK41" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL41" t="n">
         <v>0.6</v>
@@ -28897,7 +29085,7 @@
         <v>1</v>
       </c>
       <c r="EP41" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ41" t="n">
         <v>0.6</v>
@@ -29132,6 +29320,11 @@
       </c>
       <c r="HP41" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ41" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -29529,7 +29722,7 @@
         <v>0.6</v>
       </c>
       <c r="DV42" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW42" t="n">
         <v>0</v>
@@ -29574,7 +29767,7 @@
         <v>1</v>
       </c>
       <c r="EK42" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL42" t="n">
         <v>0.6</v>
@@ -29589,7 +29782,7 @@
         <v>1</v>
       </c>
       <c r="EP42" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ42" t="n">
         <v>0.6</v>
@@ -29824,6 +30017,11 @@
       </c>
       <c r="HP42" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ42" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -29859,7 +30057,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -30196,7 +30394,7 @@
       </c>
       <c r="DN43" t="inlineStr"/>
       <c r="DO43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP43" t="n">
         <v>2020</v>
@@ -30211,13 +30409,13 @@
         <v>129</v>
       </c>
       <c r="DT43" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU43" t="n">
         <v>0.6</v>
       </c>
       <c r="DV43" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW43" t="n">
         <v>1</v>
@@ -30262,7 +30460,7 @@
         <v>1</v>
       </c>
       <c r="EK43" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL43" t="n">
         <v>0.6</v>
@@ -30277,7 +30475,7 @@
         <v>0</v>
       </c>
       <c r="EP43" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ43" t="n">
         <v>0.6</v>
@@ -30512,6 +30710,11 @@
       </c>
       <c r="HP43" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ43" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -30547,7 +30750,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -30657,11 +30860,11 @@
         <v>0.5161289999999999</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
         <v>3.6</v>
@@ -31204,6 +31407,11 @@
       </c>
       <c r="HP44" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ44" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -31239,7 +31447,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -31576,10 +31784,10 @@
       </c>
       <c r="DN45" t="inlineStr"/>
       <c r="DO45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP45" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ45" t="n">
         <v>2025</v>
@@ -31597,7 +31805,7 @@
         <v>0.6</v>
       </c>
       <c r="DV45" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW45" t="n">
         <v>0</v>
@@ -31642,7 +31850,7 @@
         <v>1</v>
       </c>
       <c r="EK45" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL45" t="n">
         <v>0.6</v>
@@ -31657,7 +31865,7 @@
         <v>0</v>
       </c>
       <c r="EP45" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ45" t="n">
         <v>0.6</v>
@@ -31892,6 +32100,11 @@
       </c>
       <c r="HP45" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ45" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -31927,7 +32140,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -32289,7 +32502,7 @@
         <v>0.6</v>
       </c>
       <c r="DV46" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW46" t="n">
         <v>1</v>
@@ -32334,7 +32547,7 @@
         <v>1</v>
       </c>
       <c r="EK46" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL46" t="n">
         <v>0.6</v>
@@ -32349,7 +32562,7 @@
         <v>1</v>
       </c>
       <c r="EP46" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ46" t="n">
         <v>0.6</v>
@@ -32584,6 +32797,11 @@
       </c>
       <c r="HP46" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ46" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -32981,7 +33199,7 @@
         <v>0.6</v>
       </c>
       <c r="DV47" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW47" t="n">
         <v>0</v>
@@ -33026,7 +33244,7 @@
         <v>1</v>
       </c>
       <c r="EK47" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL47" t="n">
         <v>0.6</v>
@@ -33041,7 +33259,7 @@
         <v>1</v>
       </c>
       <c r="EP47" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ47" t="n">
         <v>0.6</v>
@@ -33276,6 +33494,11 @@
       </c>
       <c r="HP47" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ47" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -33311,7 +33534,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -33648,7 +33871,7 @@
       </c>
       <c r="DN48" t="inlineStr"/>
       <c r="DO48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP48" t="n">
         <v>2020</v>
@@ -33663,13 +33886,13 @@
         <v>129</v>
       </c>
       <c r="DT48" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU48" t="n">
         <v>0.6</v>
       </c>
       <c r="DV48" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW48" t="n">
         <v>1</v>
@@ -33714,7 +33937,7 @@
         <v>1</v>
       </c>
       <c r="EK48" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL48" t="n">
         <v>0.6</v>
@@ -33729,7 +33952,7 @@
         <v>0</v>
       </c>
       <c r="EP48" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ48" t="n">
         <v>0.6</v>
@@ -33964,6 +34187,11 @@
       </c>
       <c r="HP48" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ48" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -33999,7 +34227,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -34109,11 +34337,11 @@
         <v>0.354839</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
         <v>3.5</v>
@@ -34656,6 +34884,11 @@
       </c>
       <c r="HP49" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ49" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -34691,7 +34924,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -35028,10 +35261,10 @@
       </c>
       <c r="DN50" t="inlineStr"/>
       <c r="DO50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP50" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ50" t="n">
         <v>2025</v>
@@ -35049,7 +35282,7 @@
         <v>0.6</v>
       </c>
       <c r="DV50" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW50" t="n">
         <v>0</v>
@@ -35094,7 +35327,7 @@
         <v>1</v>
       </c>
       <c r="EK50" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL50" t="n">
         <v>0.6</v>
@@ -35109,7 +35342,7 @@
         <v>0</v>
       </c>
       <c r="EP50" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ50" t="n">
         <v>0.6</v>
@@ -35344,6 +35577,11 @@
       </c>
       <c r="HP50" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ50" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -35379,7 +35617,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -35741,7 +35979,7 @@
         <v>0.6</v>
       </c>
       <c r="DV51" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW51" t="n">
         <v>1</v>
@@ -35786,7 +36024,7 @@
         <v>1</v>
       </c>
       <c r="EK51" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL51" t="n">
         <v>0.6</v>
@@ -35801,7 +36039,7 @@
         <v>1</v>
       </c>
       <c r="EP51" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ51" t="n">
         <v>0.6</v>
@@ -36036,6 +36274,11 @@
       </c>
       <c r="HP51" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ51" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -36433,7 +36676,7 @@
         <v>0.6</v>
       </c>
       <c r="DV52" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW52" t="n">
         <v>0</v>
@@ -36478,7 +36721,7 @@
         <v>1</v>
       </c>
       <c r="EK52" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL52" t="n">
         <v>0.6</v>
@@ -36493,7 +36736,7 @@
         <v>1</v>
       </c>
       <c r="EP52" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ52" t="n">
         <v>0.6</v>
@@ -36728,6 +36971,11 @@
       </c>
       <c r="HP52" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ52" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -36763,7 +37011,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -37100,7 +37348,7 @@
       </c>
       <c r="DN53" t="inlineStr"/>
       <c r="DO53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP53" t="n">
         <v>2020</v>
@@ -37115,13 +37363,13 @@
         <v>129</v>
       </c>
       <c r="DT53" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU53" t="n">
         <v>0.6</v>
       </c>
       <c r="DV53" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW53" t="n">
         <v>1</v>
@@ -37166,7 +37414,7 @@
         <v>1</v>
       </c>
       <c r="EK53" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL53" t="n">
         <v>0.6</v>
@@ -37181,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="EP53" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ53" t="n">
         <v>0.6</v>
@@ -37416,6 +37664,11 @@
       </c>
       <c r="HP53" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ53" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -37451,7 +37704,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -37561,11 +37814,11 @@
         <v>0.642857</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
         <v>3.8</v>
@@ -38108,6 +38361,11 @@
       </c>
       <c r="HP54" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ54" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -38143,7 +38401,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -38480,10 +38738,10 @@
       </c>
       <c r="DN55" t="inlineStr"/>
       <c r="DO55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP55" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ55" t="n">
         <v>2025</v>
@@ -38501,7 +38759,7 @@
         <v>0.6</v>
       </c>
       <c r="DV55" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW55" t="n">
         <v>0</v>
@@ -38546,7 +38804,7 @@
         <v>1</v>
       </c>
       <c r="EK55" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL55" t="n">
         <v>0.6</v>
@@ -38561,7 +38819,7 @@
         <v>0</v>
       </c>
       <c r="EP55" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ55" t="n">
         <v>0.6</v>
@@ -38796,6 +39054,11 @@
       </c>
       <c r="HP55" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ55" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -38831,7 +39094,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -39193,7 +39456,7 @@
         <v>0.6</v>
       </c>
       <c r="DV56" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW56" t="n">
         <v>1</v>
@@ -39238,7 +39501,7 @@
         <v>1</v>
       </c>
       <c r="EK56" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL56" t="n">
         <v>0.6</v>
@@ -39253,7 +39516,7 @@
         <v>1</v>
       </c>
       <c r="EP56" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ56" t="n">
         <v>0.6</v>
@@ -39488,6 +39751,11 @@
       </c>
       <c r="HP56" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ56" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -39885,7 +40153,7 @@
         <v>0.6</v>
       </c>
       <c r="DV57" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW57" t="n">
         <v>0</v>
@@ -39930,7 +40198,7 @@
         <v>1</v>
       </c>
       <c r="EK57" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL57" t="n">
         <v>0.6</v>
@@ -39945,7 +40213,7 @@
         <v>1</v>
       </c>
       <c r="EP57" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ57" t="n">
         <v>0.6</v>
@@ -40180,6 +40448,11 @@
       </c>
       <c r="HP57" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ57" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -40215,7 +40488,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -40552,7 +40825,7 @@
       </c>
       <c r="DN58" t="inlineStr"/>
       <c r="DO58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP58" t="n">
         <v>2020</v>
@@ -40567,13 +40840,13 @@
         <v>129</v>
       </c>
       <c r="DT58" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU58" t="n">
         <v>0.6</v>
       </c>
       <c r="DV58" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW58" t="n">
         <v>1</v>
@@ -40618,7 +40891,7 @@
         <v>1</v>
       </c>
       <c r="EK58" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL58" t="n">
         <v>0.6</v>
@@ -40633,7 +40906,7 @@
         <v>0</v>
       </c>
       <c r="EP58" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ58" t="n">
         <v>0.6</v>
@@ -40868,6 +41141,11 @@
       </c>
       <c r="HP58" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ58" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -40903,7 +41181,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -41013,11 +41291,11 @@
         <v>0.322581</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS59" t="n">
         <v>8</v>
@@ -41560,6 +41838,11 @@
       </c>
       <c r="HP59" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ59" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -41595,7 +41878,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -41932,10 +42215,10 @@
       </c>
       <c r="DN60" t="inlineStr"/>
       <c r="DO60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP60" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ60" t="n">
         <v>2025</v>
@@ -41953,7 +42236,7 @@
         <v>0.6</v>
       </c>
       <c r="DV60" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW60" t="n">
         <v>0</v>
@@ -41998,7 +42281,7 @@
         <v>1</v>
       </c>
       <c r="EK60" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL60" t="n">
         <v>0.6</v>
@@ -42013,7 +42296,7 @@
         <v>0</v>
       </c>
       <c r="EP60" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ60" t="n">
         <v>0.6</v>
@@ -42248,6 +42531,11 @@
       </c>
       <c r="HP60" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ60" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -42283,7 +42571,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -42645,7 +42933,7 @@
         <v>0.6</v>
       </c>
       <c r="DV61" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW61" t="n">
         <v>1</v>
@@ -42690,7 +42978,7 @@
         <v>1</v>
       </c>
       <c r="EK61" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL61" t="n">
         <v>0.6</v>
@@ -42705,7 +42993,7 @@
         <v>1</v>
       </c>
       <c r="EP61" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ61" t="n">
         <v>0.6</v>
@@ -42940,6 +43228,11 @@
       </c>
       <c r="HP61" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ61" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -43337,7 +43630,7 @@
         <v>0.6</v>
       </c>
       <c r="DV62" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW62" t="n">
         <v>0</v>
@@ -43382,7 +43675,7 @@
         <v>1</v>
       </c>
       <c r="EK62" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL62" t="n">
         <v>0.6</v>
@@ -43397,7 +43690,7 @@
         <v>1</v>
       </c>
       <c r="EP62" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ62" t="n">
         <v>0.6</v>
@@ -43632,6 +43925,11 @@
       </c>
       <c r="HP62" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ62" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -43667,7 +43965,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -44004,7 +44302,7 @@
       </c>
       <c r="DN63" t="inlineStr"/>
       <c r="DO63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP63" t="n">
         <v>2020</v>
@@ -44019,13 +44317,13 @@
         <v>129</v>
       </c>
       <c r="DT63" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU63" t="n">
         <v>0.6</v>
       </c>
       <c r="DV63" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW63" t="n">
         <v>1</v>
@@ -44070,7 +44368,7 @@
         <v>1</v>
       </c>
       <c r="EK63" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL63" t="n">
         <v>0.6</v>
@@ -44085,7 +44383,7 @@
         <v>0</v>
       </c>
       <c r="EP63" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ63" t="n">
         <v>0.6</v>
@@ -44320,6 +44618,11 @@
       </c>
       <c r="HP63" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ63" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -44355,7 +44658,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -44465,11 +44768,11 @@
         <v>0.6</v>
       </c>
       <c r="AP64" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS64" t="n">
         <v>12.4</v>
@@ -45012,6 +45315,11 @@
       </c>
       <c r="HP64" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ64" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -45047,7 +45355,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -45384,10 +45692,10 @@
       </c>
       <c r="DN65" t="inlineStr"/>
       <c r="DO65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP65" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ65" t="n">
         <v>2025</v>
@@ -45405,7 +45713,7 @@
         <v>0.6</v>
       </c>
       <c r="DV65" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW65" t="n">
         <v>0</v>
@@ -45450,7 +45758,7 @@
         <v>1</v>
       </c>
       <c r="EK65" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL65" t="n">
         <v>0.6</v>
@@ -45465,7 +45773,7 @@
         <v>0</v>
       </c>
       <c r="EP65" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ65" t="n">
         <v>0.6</v>
@@ -45700,6 +46008,11 @@
       </c>
       <c r="HP65" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ65" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -45735,7 +46048,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -46097,7 +46410,7 @@
         <v>0.6</v>
       </c>
       <c r="DV66" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW66" t="n">
         <v>1</v>
@@ -46142,7 +46455,7 @@
         <v>1</v>
       </c>
       <c r="EK66" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL66" t="n">
         <v>0.6</v>
@@ -46157,7 +46470,7 @@
         <v>1</v>
       </c>
       <c r="EP66" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ66" t="n">
         <v>0.6</v>
@@ -46392,6 +46705,11 @@
       </c>
       <c r="HP66" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ66" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -46789,7 +47107,7 @@
         <v>0.6</v>
       </c>
       <c r="DV67" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW67" t="n">
         <v>0</v>
@@ -46834,7 +47152,7 @@
         <v>1</v>
       </c>
       <c r="EK67" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL67" t="n">
         <v>0.6</v>
@@ -46849,7 +47167,7 @@
         <v>1</v>
       </c>
       <c r="EP67" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ67" t="n">
         <v>0.6</v>
@@ -47084,6 +47402,11 @@
       </c>
       <c r="HP67" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ67" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -47119,7 +47442,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -47456,7 +47779,7 @@
       </c>
       <c r="DN68" t="inlineStr"/>
       <c r="DO68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP68" t="n">
         <v>2020</v>
@@ -47471,13 +47794,13 @@
         <v>129</v>
       </c>
       <c r="DT68" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU68" t="n">
         <v>0.6</v>
       </c>
       <c r="DV68" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW68" t="n">
         <v>1</v>
@@ -47522,7 +47845,7 @@
         <v>1</v>
       </c>
       <c r="EK68" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL68" t="n">
         <v>0.6</v>
@@ -47537,7 +47860,7 @@
         <v>0</v>
       </c>
       <c r="EP68" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ68" t="n">
         <v>0.6</v>
@@ -47772,6 +48095,11 @@
       </c>
       <c r="HP68" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ68" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -47807,7 +48135,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -47917,11 +48245,11 @@
         <v>0.387097</v>
       </c>
       <c r="AP69" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ69" t="inlineStr"/>
       <c r="AR69" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS69" t="n">
         <v>16.3</v>
@@ -48464,6 +48792,11 @@
       </c>
       <c r="HP69" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ69" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -48499,7 +48832,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -48836,10 +49169,10 @@
       </c>
       <c r="DN70" t="inlineStr"/>
       <c r="DO70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP70" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ70" t="n">
         <v>2025</v>
@@ -48857,7 +49190,7 @@
         <v>0.6</v>
       </c>
       <c r="DV70" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW70" t="n">
         <v>0</v>
@@ -48902,7 +49235,7 @@
         <v>1</v>
       </c>
       <c r="EK70" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL70" t="n">
         <v>0.6</v>
@@ -48917,7 +49250,7 @@
         <v>0</v>
       </c>
       <c r="EP70" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ70" t="n">
         <v>0.6</v>
@@ -49152,6 +49485,11 @@
       </c>
       <c r="HP70" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ70" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -49187,7 +49525,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -49549,7 +49887,7 @@
         <v>0.6</v>
       </c>
       <c r="DV71" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW71" t="n">
         <v>1</v>
@@ -49594,7 +49932,7 @@
         <v>1</v>
       </c>
       <c r="EK71" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL71" t="n">
         <v>0.6</v>
@@ -49609,7 +49947,7 @@
         <v>1</v>
       </c>
       <c r="EP71" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ71" t="n">
         <v>0.6</v>
@@ -49844,6 +50182,11 @@
       </c>
       <c r="HP71" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ71" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -50241,7 +50584,7 @@
         <v>0.6</v>
       </c>
       <c r="DV72" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW72" t="n">
         <v>0</v>
@@ -50286,7 +50629,7 @@
         <v>1</v>
       </c>
       <c r="EK72" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL72" t="n">
         <v>0.6</v>
@@ -50301,7 +50644,7 @@
         <v>1</v>
       </c>
       <c r="EP72" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ72" t="n">
         <v>0.6</v>
@@ -50536,6 +50879,11 @@
       </c>
       <c r="HP72" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ72" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -50571,7 +50919,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -50908,7 +51256,7 @@
       </c>
       <c r="DN73" t="inlineStr"/>
       <c r="DO73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP73" t="n">
         <v>2020</v>
@@ -50923,13 +51271,13 @@
         <v>129</v>
       </c>
       <c r="DT73" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU73" t="n">
         <v>0.6</v>
       </c>
       <c r="DV73" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW73" t="n">
         <v>1</v>
@@ -50974,7 +51322,7 @@
         <v>1</v>
       </c>
       <c r="EK73" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL73" t="n">
         <v>0.6</v>
@@ -50989,7 +51337,7 @@
         <v>0</v>
       </c>
       <c r="EP73" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ73" t="n">
         <v>0.6</v>
@@ -51224,6 +51572,11 @@
       </c>
       <c r="HP73" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ73" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -51259,7 +51612,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -51369,11 +51722,11 @@
         <v>0.333333</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ74" t="inlineStr"/>
       <c r="AR74" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS74" t="n">
         <v>22</v>
@@ -51916,6 +52269,11 @@
       </c>
       <c r="HP74" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ74" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -51951,7 +52309,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -52288,10 +52646,10 @@
       </c>
       <c r="DN75" t="inlineStr"/>
       <c r="DO75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP75" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ75" t="n">
         <v>2025</v>
@@ -52309,7 +52667,7 @@
         <v>0.6</v>
       </c>
       <c r="DV75" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW75" t="n">
         <v>0</v>
@@ -52354,7 +52712,7 @@
         <v>1</v>
       </c>
       <c r="EK75" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL75" t="n">
         <v>0.6</v>
@@ -52369,7 +52727,7 @@
         <v>0</v>
       </c>
       <c r="EP75" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ75" t="n">
         <v>0.6</v>
@@ -52604,6 +52962,11 @@
       </c>
       <c r="HP75" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ75" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -52639,7 +53002,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -53001,7 +53364,7 @@
         <v>0.6</v>
       </c>
       <c r="DV76" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW76" t="n">
         <v>1</v>
@@ -53046,7 +53409,7 @@
         <v>1</v>
       </c>
       <c r="EK76" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL76" t="n">
         <v>0.6</v>
@@ -53061,7 +53424,7 @@
         <v>1</v>
       </c>
       <c r="EP76" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ76" t="n">
         <v>0.6</v>
@@ -53296,6 +53659,11 @@
       </c>
       <c r="HP76" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ76" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -53693,7 +54061,7 @@
         <v>0.6</v>
       </c>
       <c r="DV77" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW77" t="n">
         <v>0</v>
@@ -53738,7 +54106,7 @@
         <v>1</v>
       </c>
       <c r="EK77" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL77" t="n">
         <v>0.6</v>
@@ -53753,7 +54121,7 @@
         <v>1</v>
       </c>
       <c r="EP77" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ77" t="n">
         <v>0.6</v>
@@ -53988,6 +54356,11 @@
       </c>
       <c r="HP77" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ77" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -54023,7 +54396,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -54360,7 +54733,7 @@
       </c>
       <c r="DN78" t="inlineStr"/>
       <c r="DO78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP78" t="n">
         <v>2020</v>
@@ -54375,13 +54748,13 @@
         <v>129</v>
       </c>
       <c r="DT78" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU78" t="n">
         <v>0.6</v>
       </c>
       <c r="DV78" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW78" t="n">
         <v>1</v>
@@ -54426,7 +54799,7 @@
         <v>1</v>
       </c>
       <c r="EK78" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL78" t="n">
         <v>0.6</v>
@@ -54441,7 +54814,7 @@
         <v>0</v>
       </c>
       <c r="EP78" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ78" t="n">
         <v>0.6</v>
@@ -54676,6 +55049,11 @@
       </c>
       <c r="HP78" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ78" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -54711,7 +55089,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -54821,11 +55199,11 @@
         <v>0.870968</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ79" t="inlineStr"/>
       <c r="AR79" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS79" t="n">
         <v>20.6</v>
@@ -55368,6 +55746,11 @@
       </c>
       <c r="HP79" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ79" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -55403,7 +55786,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -55740,10 +56123,10 @@
       </c>
       <c r="DN80" t="inlineStr"/>
       <c r="DO80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP80" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ80" t="n">
         <v>2025</v>
@@ -55761,7 +56144,7 @@
         <v>0.6</v>
       </c>
       <c r="DV80" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW80" t="n">
         <v>0</v>
@@ -55806,7 +56189,7 @@
         <v>1</v>
       </c>
       <c r="EK80" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL80" t="n">
         <v>0.6</v>
@@ -55821,7 +56204,7 @@
         <v>0</v>
       </c>
       <c r="EP80" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ80" t="n">
         <v>0.6</v>
@@ -56056,6 +56439,11 @@
       </c>
       <c r="HP80" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ80" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -56091,7 +56479,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -56453,7 +56841,7 @@
         <v>0.6</v>
       </c>
       <c r="DV81" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW81" t="n">
         <v>1</v>
@@ -56498,7 +56886,7 @@
         <v>1</v>
       </c>
       <c r="EK81" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL81" t="n">
         <v>0.6</v>
@@ -56513,7 +56901,7 @@
         <v>1</v>
       </c>
       <c r="EP81" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ81" t="n">
         <v>0.6</v>
@@ -56748,6 +57136,11 @@
       </c>
       <c r="HP81" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ81" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -57145,7 +57538,7 @@
         <v>0.6</v>
       </c>
       <c r="DV82" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW82" t="n">
         <v>0</v>
@@ -57190,7 +57583,7 @@
         <v>1</v>
       </c>
       <c r="EK82" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL82" t="n">
         <v>0.6</v>
@@ -57205,7 +57598,7 @@
         <v>1</v>
       </c>
       <c r="EP82" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ82" t="n">
         <v>0.6</v>
@@ -57440,6 +57833,11 @@
       </c>
       <c r="HP82" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ82" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -57475,7 +57873,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -57812,7 +58210,7 @@
       </c>
       <c r="DN83" t="inlineStr"/>
       <c r="DO83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP83" t="n">
         <v>2020</v>
@@ -57827,13 +58225,13 @@
         <v>129</v>
       </c>
       <c r="DT83" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU83" t="n">
         <v>0.6</v>
       </c>
       <c r="DV83" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW83" t="n">
         <v>1</v>
@@ -57878,7 +58276,7 @@
         <v>1</v>
       </c>
       <c r="EK83" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL83" t="n">
         <v>0.6</v>
@@ -57893,7 +58291,7 @@
         <v>0</v>
       </c>
       <c r="EP83" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ83" t="n">
         <v>0.6</v>
@@ -58128,6 +58526,11 @@
       </c>
       <c r="HP83" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ83" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -58163,7 +58566,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -58273,11 +58676,11 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ84" t="inlineStr"/>
       <c r="AR84" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS84" t="n">
         <v>20.6</v>
@@ -58820,6 +59223,11 @@
       </c>
       <c r="HP84" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ84" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -58855,7 +59263,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -59192,10 +59600,10 @@
       </c>
       <c r="DN85" t="inlineStr"/>
       <c r="DO85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP85" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ85" t="n">
         <v>2025</v>
@@ -59213,7 +59621,7 @@
         <v>0.6</v>
       </c>
       <c r="DV85" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW85" t="n">
         <v>0</v>
@@ -59258,7 +59666,7 @@
         <v>1</v>
       </c>
       <c r="EK85" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL85" t="n">
         <v>0.6</v>
@@ -59273,7 +59681,7 @@
         <v>0</v>
       </c>
       <c r="EP85" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ85" t="n">
         <v>0.6</v>
@@ -59508,6 +59916,11 @@
       </c>
       <c r="HP85" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ85" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -59543,7 +59956,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -59905,7 +60318,7 @@
         <v>0.6</v>
       </c>
       <c r="DV86" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW86" t="n">
         <v>1</v>
@@ -59950,7 +60363,7 @@
         <v>1</v>
       </c>
       <c r="EK86" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL86" t="n">
         <v>0.6</v>
@@ -59965,7 +60378,7 @@
         <v>1</v>
       </c>
       <c r="EP86" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ86" t="n">
         <v>0.6</v>
@@ -60200,6 +60613,11 @@
       </c>
       <c r="HP86" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ86" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -60597,7 +61015,7 @@
         <v>0.6</v>
       </c>
       <c r="DV87" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW87" t="n">
         <v>0</v>
@@ -60642,7 +61060,7 @@
         <v>1</v>
       </c>
       <c r="EK87" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL87" t="n">
         <v>0.6</v>
@@ -60657,7 +61075,7 @@
         <v>1</v>
       </c>
       <c r="EP87" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ87" t="n">
         <v>0.6</v>
@@ -60892,6 +61310,11 @@
       </c>
       <c r="HP87" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ87" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -60927,7 +61350,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -61264,7 +61687,7 @@
       </c>
       <c r="DN88" t="inlineStr"/>
       <c r="DO88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP88" t="n">
         <v>2020</v>
@@ -61279,13 +61702,13 @@
         <v>129</v>
       </c>
       <c r="DT88" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU88" t="n">
         <v>0.6</v>
       </c>
       <c r="DV88" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW88" t="n">
         <v>1</v>
@@ -61330,7 +61753,7 @@
         <v>1</v>
       </c>
       <c r="EK88" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL88" t="n">
         <v>0.6</v>
@@ -61345,7 +61768,7 @@
         <v>0</v>
       </c>
       <c r="EP88" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ88" t="n">
         <v>0.6</v>
@@ -61580,6 +62003,11 @@
       </c>
       <c r="HP88" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ88" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -61615,7 +62043,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -61725,11 +62153,11 @@
         <v>0.266667</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS89" t="n">
         <v>15.7</v>
@@ -62272,6 +62700,11 @@
       </c>
       <c r="HP89" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ89" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -62307,7 +62740,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -62644,10 +63077,10 @@
       </c>
       <c r="DN90" t="inlineStr"/>
       <c r="DO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP90" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ90" t="n">
         <v>2025</v>
@@ -62665,7 +63098,7 @@
         <v>0.6</v>
       </c>
       <c r="DV90" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW90" t="n">
         <v>0</v>
@@ -62710,7 +63143,7 @@
         <v>1</v>
       </c>
       <c r="EK90" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL90" t="n">
         <v>0.6</v>
@@ -62725,7 +63158,7 @@
         <v>0</v>
       </c>
       <c r="EP90" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ90" t="n">
         <v>0.6</v>
@@ -62960,6 +63393,11 @@
       </c>
       <c r="HP90" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ90" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -62995,7 +63433,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -63357,7 +63795,7 @@
         <v>0.6</v>
       </c>
       <c r="DV91" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW91" t="n">
         <v>1</v>
@@ -63402,7 +63840,7 @@
         <v>1</v>
       </c>
       <c r="EK91" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL91" t="n">
         <v>0.6</v>
@@ -63417,7 +63855,7 @@
         <v>1</v>
       </c>
       <c r="EP91" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ91" t="n">
         <v>0.6</v>
@@ -63652,6 +64090,11 @@
       </c>
       <c r="HP91" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ91" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -64049,7 +64492,7 @@
         <v>0.6</v>
       </c>
       <c r="DV92" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW92" t="n">
         <v>0</v>
@@ -64094,7 +64537,7 @@
         <v>1</v>
       </c>
       <c r="EK92" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL92" t="n">
         <v>0.6</v>
@@ -64109,7 +64552,7 @@
         <v>1</v>
       </c>
       <c r="EP92" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ92" t="n">
         <v>0.6</v>
@@ -64344,6 +64787,11 @@
       </c>
       <c r="HP92" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ92" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -64379,7 +64827,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -64716,7 +65164,7 @@
       </c>
       <c r="DN93" t="inlineStr"/>
       <c r="DO93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP93" t="n">
         <v>2020</v>
@@ -64731,13 +65179,13 @@
         <v>129</v>
       </c>
       <c r="DT93" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU93" t="n">
         <v>0.6</v>
       </c>
       <c r="DV93" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW93" t="n">
         <v>1</v>
@@ -64782,7 +65230,7 @@
         <v>1</v>
       </c>
       <c r="EK93" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL93" t="n">
         <v>0.6</v>
@@ -64797,7 +65245,7 @@
         <v>0</v>
       </c>
       <c r="EP93" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ93" t="n">
         <v>0.6</v>
@@ -65032,6 +65480,11 @@
       </c>
       <c r="HP93" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ93" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -65067,7 +65520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -65177,11 +65630,11 @@
         <v>0.580645</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ94" t="inlineStr"/>
       <c r="AR94" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS94" t="n">
         <v>11.5</v>
@@ -65724,6 +66177,11 @@
       </c>
       <c r="HP94" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ94" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -65759,7 +66217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -66096,10 +66554,10 @@
       </c>
       <c r="DN95" t="inlineStr"/>
       <c r="DO95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP95" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ95" t="n">
         <v>2025</v>
@@ -66117,7 +66575,7 @@
         <v>0.6</v>
       </c>
       <c r="DV95" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW95" t="n">
         <v>0</v>
@@ -66162,7 +66620,7 @@
         <v>1</v>
       </c>
       <c r="EK95" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL95" t="n">
         <v>0.6</v>
@@ -66177,7 +66635,7 @@
         <v>0</v>
       </c>
       <c r="EP95" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ95" t="n">
         <v>0.6</v>
@@ -66412,6 +66870,11 @@
       </c>
       <c r="HP95" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ95" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -66447,7 +66910,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -66809,7 +67272,7 @@
         <v>0.6</v>
       </c>
       <c r="DV96" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW96" t="n">
         <v>1</v>
@@ -66854,7 +67317,7 @@
         <v>1</v>
       </c>
       <c r="EK96" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL96" t="n">
         <v>0.6</v>
@@ -66869,7 +67332,7 @@
         <v>1</v>
       </c>
       <c r="EP96" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ96" t="n">
         <v>0.6</v>
@@ -67104,6 +67567,11 @@
       </c>
       <c r="HP96" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ96" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -67501,7 +67969,7 @@
         <v>0.6</v>
       </c>
       <c r="DV97" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW97" t="n">
         <v>0</v>
@@ -67546,7 +68014,7 @@
         <v>1</v>
       </c>
       <c r="EK97" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL97" t="n">
         <v>0.6</v>
@@ -67561,7 +68029,7 @@
         <v>1</v>
       </c>
       <c r="EP97" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ97" t="n">
         <v>0.6</v>
@@ -67796,6 +68264,11 @@
       </c>
       <c r="HP97" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ97" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -67831,7 +68304,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -68168,7 +68641,7 @@
       </c>
       <c r="DN98" t="inlineStr"/>
       <c r="DO98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP98" t="n">
         <v>2020</v>
@@ -68183,13 +68656,13 @@
         <v>129</v>
       </c>
       <c r="DT98" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU98" t="n">
         <v>0.6</v>
       </c>
       <c r="DV98" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW98" t="n">
         <v>1</v>
@@ -68234,7 +68707,7 @@
         <v>1</v>
       </c>
       <c r="EK98" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL98" t="n">
         <v>0.6</v>
@@ -68249,7 +68722,7 @@
         <v>0</v>
       </c>
       <c r="EP98" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ98" t="n">
         <v>0.6</v>
@@ -68484,6 +68957,11 @@
       </c>
       <c r="HP98" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ98" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -68519,7 +68997,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -68629,11 +69107,11 @@
         <v>0.366667</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ99" t="inlineStr"/>
       <c r="AR99" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS99" t="n">
         <v>5.6</v>
@@ -69176,6 +69654,11 @@
       </c>
       <c r="HP99" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ99" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -69211,7 +69694,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -69548,10 +70031,10 @@
       </c>
       <c r="DN100" t="inlineStr"/>
       <c r="DO100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP100" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ100" t="n">
         <v>2025</v>
@@ -69569,7 +70052,7 @@
         <v>0.6</v>
       </c>
       <c r="DV100" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW100" t="n">
         <v>0</v>
@@ -69614,7 +70097,7 @@
         <v>1</v>
       </c>
       <c r="EK100" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL100" t="n">
         <v>0.6</v>
@@ -69629,7 +70112,7 @@
         <v>0</v>
       </c>
       <c r="EP100" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ100" t="n">
         <v>0.6</v>
@@ -69864,6 +70347,11 @@
       </c>
       <c r="HP100" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ100" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -69899,7 +70387,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -70261,7 +70749,7 @@
         <v>0.6</v>
       </c>
       <c r="DV101" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW101" t="n">
         <v>1</v>
@@ -70306,7 +70794,7 @@
         <v>1</v>
       </c>
       <c r="EK101" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL101" t="n">
         <v>0.6</v>
@@ -70321,7 +70809,7 @@
         <v>1</v>
       </c>
       <c r="EP101" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ101" t="n">
         <v>0.6</v>
@@ -70556,6 +71044,11 @@
       </c>
       <c r="HP101" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ101" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -70953,7 +71446,7 @@
         <v>0.6</v>
       </c>
       <c r="DV102" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW102" t="n">
         <v>0</v>
@@ -70998,7 +71491,7 @@
         <v>1</v>
       </c>
       <c r="EK102" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL102" t="n">
         <v>0.6</v>
@@ -71013,7 +71506,7 @@
         <v>1</v>
       </c>
       <c r="EP102" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ102" t="n">
         <v>0.6</v>
@@ -71248,6 +71741,11 @@
       </c>
       <c r="HP102" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ102" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -71283,7 +71781,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -71620,7 +72118,7 @@
       </c>
       <c r="DN103" t="inlineStr"/>
       <c r="DO103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP103" t="n">
         <v>2020</v>
@@ -71635,13 +72133,13 @@
         <v>129</v>
       </c>
       <c r="DT103" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU103" t="n">
         <v>0.6</v>
       </c>
       <c r="DV103" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW103" t="n">
         <v>1</v>
@@ -71686,7 +72184,7 @@
         <v>1</v>
       </c>
       <c r="EK103" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL103" t="n">
         <v>0.6</v>
@@ -71701,7 +72199,7 @@
         <v>0</v>
       </c>
       <c r="EP103" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ103" t="n">
         <v>0.6</v>
@@ -71936,6 +72434,11 @@
       </c>
       <c r="HP103" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ103" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -71971,7 +72474,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -72081,11 +72584,11 @@
         <v>0.5161289999999999</v>
       </c>
       <c r="AP104" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AQ104" t="inlineStr"/>
       <c r="AR104" t="n">
-        <v>4.235294117647059</v>
+        <v>0</v>
       </c>
       <c r="AS104" t="n">
         <v>3.8</v>
@@ -72628,6 +73131,11 @@
       </c>
       <c r="HP104" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ104" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -72663,7 +73171,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -73000,10 +73508,10 @@
       </c>
       <c r="DN105" t="inlineStr"/>
       <c r="DO105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP105" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ105" t="n">
         <v>2025</v>
@@ -73021,7 +73529,7 @@
         <v>0.6</v>
       </c>
       <c r="DV105" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW105" t="n">
         <v>0</v>
@@ -73066,7 +73574,7 @@
         <v>1</v>
       </c>
       <c r="EK105" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL105" t="n">
         <v>0.6</v>
@@ -73081,7 +73589,7 @@
         <v>0</v>
       </c>
       <c r="EP105" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ105" t="n">
         <v>0.6</v>
@@ -73316,6 +73824,11 @@
       </c>
       <c r="HP105" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ105" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -73351,7 +73864,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -73713,7 +74226,7 @@
         <v>0.6</v>
       </c>
       <c r="DV106" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW106" t="n">
         <v>1</v>
@@ -73758,7 +74271,7 @@
         <v>1</v>
       </c>
       <c r="EK106" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL106" t="n">
         <v>0.6</v>
@@ -73773,7 +74286,7 @@
         <v>1</v>
       </c>
       <c r="EP106" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ106" t="n">
         <v>0.6</v>
@@ -74008,6 +74521,11 @@
       </c>
       <c r="HP106" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ106" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -74405,7 +74923,7 @@
         <v>0.6</v>
       </c>
       <c r="DV107" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW107" t="n">
         <v>0</v>
@@ -74450,7 +74968,7 @@
         <v>1</v>
       </c>
       <c r="EK107" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL107" t="n">
         <v>0.6</v>
@@ -74465,7 +74983,7 @@
         <v>1</v>
       </c>
       <c r="EP107" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ107" t="n">
         <v>0.6</v>
@@ -74700,6 +75218,11 @@
       </c>
       <c r="HP107" t="n">
         <v>0</v>
+      </c>
+      <c r="HQ107" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -74735,7 +75258,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -75072,7 +75595,7 @@
       </c>
       <c r="DN108" t="inlineStr"/>
       <c r="DO108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP108" t="n">
         <v>2020</v>
@@ -75087,13 +75610,13 @@
         <v>129</v>
       </c>
       <c r="DT108" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU108" t="n">
         <v>0.6</v>
       </c>
       <c r="DV108" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW108" t="n">
         <v>1</v>
@@ -75138,7 +75661,7 @@
         <v>1</v>
       </c>
       <c r="EK108" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL108" t="n">
         <v>0.6</v>
@@ -75153,7 +75676,7 @@
         <v>0</v>
       </c>
       <c r="EP108" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ108" t="n">
         <v>0.6</v>
@@ -75388,6 +75911,11 @@
       </c>
       <c r="HP108" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ108" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -75423,7 +75951,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -76084,6 +76612,11 @@
       </c>
       <c r="HP109" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ109" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -76119,7 +76652,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -76456,10 +76989,10 @@
       </c>
       <c r="DN110" t="inlineStr"/>
       <c r="DO110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP110" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ110" t="n">
         <v>2025</v>
@@ -76477,7 +77010,7 @@
         <v>0.6</v>
       </c>
       <c r="DV110" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW110" t="n">
         <v>0</v>
@@ -76522,7 +77055,7 @@
         <v>1</v>
       </c>
       <c r="EK110" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL110" t="n">
         <v>0.6</v>
@@ -76537,7 +77070,7 @@
         <v>0</v>
       </c>
       <c r="EP110" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ110" t="n">
         <v>0.6</v>
@@ -76772,6 +77305,11 @@
       </c>
       <c r="HP110" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ110" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -76807,7 +77345,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -77169,7 +77707,7 @@
         <v>0.6</v>
       </c>
       <c r="DV111" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW111" t="n">
         <v>1</v>
@@ -77214,7 +77752,7 @@
         <v>1</v>
       </c>
       <c r="EK111" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL111" t="n">
         <v>0.6</v>
@@ -77229,7 +77767,7 @@
         <v>1</v>
       </c>
       <c r="EP111" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ111" t="n">
         <v>0.6</v>
@@ -77464,6 +78002,11 @@
       </c>
       <c r="HP111" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ111" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -77861,7 +78404,7 @@
         <v>0.6</v>
       </c>
       <c r="DV112" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW112" t="n">
         <v>0</v>
@@ -77906,7 +78449,7 @@
         <v>1</v>
       </c>
       <c r="EK112" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL112" t="n">
         <v>0.6</v>
@@ -77921,7 +78464,7 @@
         <v>1</v>
       </c>
       <c r="EP112" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ112" t="n">
         <v>0.6</v>
@@ -78156,6 +78699,11 @@
       </c>
       <c r="HP112" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ112" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -78191,7 +78739,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -78528,7 +79076,7 @@
       </c>
       <c r="DN113" t="inlineStr"/>
       <c r="DO113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP113" t="n">
         <v>2020</v>
@@ -78543,13 +79091,13 @@
         <v>129</v>
       </c>
       <c r="DT113" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU113" t="n">
         <v>0.6</v>
       </c>
       <c r="DV113" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW113" t="n">
         <v>1</v>
@@ -78594,7 +79142,7 @@
         <v>1</v>
       </c>
       <c r="EK113" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL113" t="n">
         <v>0.6</v>
@@ -78609,7 +79157,7 @@
         <v>0</v>
       </c>
       <c r="EP113" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ113" t="n">
         <v>0.6</v>
@@ -78844,6 +79392,11 @@
       </c>
       <c r="HP113" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ113" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -78879,7 +79432,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -79540,6 +80093,11 @@
       </c>
       <c r="HP114" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ114" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -79575,7 +80133,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -79912,10 +80470,10 @@
       </c>
       <c r="DN115" t="inlineStr"/>
       <c r="DO115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP115" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ115" t="n">
         <v>2025</v>
@@ -79933,7 +80491,7 @@
         <v>0.6</v>
       </c>
       <c r="DV115" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW115" t="n">
         <v>0</v>
@@ -79978,7 +80536,7 @@
         <v>1</v>
       </c>
       <c r="EK115" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL115" t="n">
         <v>0.6</v>
@@ -79993,7 +80551,7 @@
         <v>0</v>
       </c>
       <c r="EP115" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ115" t="n">
         <v>0.6</v>
@@ -80228,6 +80786,11 @@
       </c>
       <c r="HP115" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ115" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -80263,7 +80826,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -80625,7 +81188,7 @@
         <v>0.6</v>
       </c>
       <c r="DV116" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW116" t="n">
         <v>1</v>
@@ -80670,7 +81233,7 @@
         <v>1</v>
       </c>
       <c r="EK116" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL116" t="n">
         <v>0.6</v>
@@ -80685,7 +81248,7 @@
         <v>1</v>
       </c>
       <c r="EP116" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ116" t="n">
         <v>0.6</v>
@@ -80920,6 +81483,11 @@
       </c>
       <c r="HP116" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ116" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -81317,7 +81885,7 @@
         <v>0.6</v>
       </c>
       <c r="DV117" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW117" t="n">
         <v>0</v>
@@ -81362,7 +81930,7 @@
         <v>1</v>
       </c>
       <c r="EK117" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL117" t="n">
         <v>0.6</v>
@@ -81377,7 +81945,7 @@
         <v>1</v>
       </c>
       <c r="EP117" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ117" t="n">
         <v>0.6</v>
@@ -81612,6 +82180,11 @@
       </c>
       <c r="HP117" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ117" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -81647,7 +82220,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -81984,7 +82557,7 @@
       </c>
       <c r="DN118" t="inlineStr"/>
       <c r="DO118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP118" t="n">
         <v>2020</v>
@@ -81999,13 +82572,13 @@
         <v>129</v>
       </c>
       <c r="DT118" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU118" t="n">
         <v>0.6</v>
       </c>
       <c r="DV118" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW118" t="n">
         <v>1</v>
@@ -82050,7 +82623,7 @@
         <v>1</v>
       </c>
       <c r="EK118" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL118" t="n">
         <v>0.6</v>
@@ -82065,7 +82638,7 @@
         <v>0</v>
       </c>
       <c r="EP118" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ118" t="n">
         <v>0.6</v>
@@ -82300,6 +82873,11 @@
       </c>
       <c r="HP118" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ118" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -82335,7 +82913,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -82996,6 +83574,11 @@
       </c>
       <c r="HP119" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ119" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -83031,7 +83614,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -83368,10 +83951,10 @@
       </c>
       <c r="DN120" t="inlineStr"/>
       <c r="DO120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP120" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ120" t="n">
         <v>2025</v>
@@ -83389,7 +83972,7 @@
         <v>0.6</v>
       </c>
       <c r="DV120" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW120" t="n">
         <v>0</v>
@@ -83434,7 +84017,7 @@
         <v>1</v>
       </c>
       <c r="EK120" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL120" t="n">
         <v>0.6</v>
@@ -83449,7 +84032,7 @@
         <v>0</v>
       </c>
       <c r="EP120" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ120" t="n">
         <v>0.6</v>
@@ -83684,6 +84267,11 @@
       </c>
       <c r="HP120" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ120" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -83719,7 +84307,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -84081,7 +84669,7 @@
         <v>0.6</v>
       </c>
       <c r="DV121" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW121" t="n">
         <v>1</v>
@@ -84126,7 +84714,7 @@
         <v>1</v>
       </c>
       <c r="EK121" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL121" t="n">
         <v>0.6</v>
@@ -84141,7 +84729,7 @@
         <v>1</v>
       </c>
       <c r="EP121" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ121" t="n">
         <v>0.6</v>
@@ -84376,6 +84964,11 @@
       </c>
       <c r="HP121" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ121" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -84773,7 +85366,7 @@
         <v>0.6</v>
       </c>
       <c r="DV122" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW122" t="n">
         <v>0</v>
@@ -84818,7 +85411,7 @@
         <v>1</v>
       </c>
       <c r="EK122" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL122" t="n">
         <v>0.6</v>
@@ -84833,7 +85426,7 @@
         <v>1</v>
       </c>
       <c r="EP122" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ122" t="n">
         <v>0.6</v>
@@ -85068,6 +85661,11 @@
       </c>
       <c r="HP122" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ122" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -85103,7 +85701,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -85440,7 +86038,7 @@
       </c>
       <c r="DN123" t="inlineStr"/>
       <c r="DO123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP123" t="n">
         <v>2020</v>
@@ -85455,13 +86053,13 @@
         <v>129</v>
       </c>
       <c r="DT123" t="n">
-        <v>0.7</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="DU123" t="n">
         <v>0.6</v>
       </c>
       <c r="DV123" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW123" t="n">
         <v>1</v>
@@ -85506,7 +86104,7 @@
         <v>1</v>
       </c>
       <c r="EK123" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL123" t="n">
         <v>0.6</v>
@@ -85521,7 +86119,7 @@
         <v>0</v>
       </c>
       <c r="EP123" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ123" t="n">
         <v>0.6</v>
@@ -85756,6 +86354,11 @@
       </c>
       <c r="HP123" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ123" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -85791,7 +86394,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -86452,6 +87055,11 @@
       </c>
       <c r="HP124" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ124" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -86487,7 +87095,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -86824,10 +87432,10 @@
       </c>
       <c r="DN125" t="inlineStr"/>
       <c r="DO125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP125" t="n">
-        <v>1995.904761904762</v>
+        <v>1976</v>
       </c>
       <c r="DQ125" t="n">
         <v>2025</v>
@@ -86845,7 +87453,7 @@
         <v>0.6</v>
       </c>
       <c r="DV125" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW125" t="n">
         <v>0</v>
@@ -86890,7 +87498,7 @@
         <v>1</v>
       </c>
       <c r="EK125" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL125" t="n">
         <v>0.6</v>
@@ -86905,7 +87513,7 @@
         <v>0</v>
       </c>
       <c r="EP125" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ125" t="n">
         <v>0.6</v>
@@ -87140,6 +87748,11 @@
       </c>
       <c r="HP125" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ125" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -87175,7 +87788,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -87537,7 +88150,7 @@
         <v>0.6</v>
       </c>
       <c r="DV126" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW126" t="n">
         <v>1</v>
@@ -87582,7 +88195,7 @@
         <v>1</v>
       </c>
       <c r="EK126" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL126" t="n">
         <v>0.6</v>
@@ -87597,7 +88210,7 @@
         <v>1</v>
       </c>
       <c r="EP126" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ126" t="n">
         <v>0.6</v>
@@ -87832,6 +88445,11 @@
       </c>
       <c r="HP126" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ126" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -88229,7 +88847,7 @@
         <v>0.6</v>
       </c>
       <c r="DV127" t="n">
-        <v>0.8</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="DW127" t="n">
         <v>0</v>
@@ -88274,7 +88892,7 @@
         <v>1</v>
       </c>
       <c r="EK127" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EL127" t="n">
         <v>0.6</v>
@@ -88289,7 +88907,7 @@
         <v>1</v>
       </c>
       <c r="EP127" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="EQ127" t="n">
         <v>0.6</v>
@@ -88524,6 +89142,11 @@
       </c>
       <c r="HP127" t="n">
         <v>1</v>
+      </c>
+      <c r="HQ127" t="inlineStr">
+        <is>
+          <t>midscale</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/accor/data/model_data.xlsx
+++ b/accor/data/model_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="model_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -26580,7 +26580,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -28663,7 +28663,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -30057,7 +30057,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -32140,7 +32140,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -34924,7 +34924,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -35617,7 +35617,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -37704,7 +37704,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -38401,7 +38401,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -39094,7 +39094,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -40488,7 +40488,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -41181,7 +41181,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -41878,7 +41878,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -43965,7 +43965,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -44658,7 +44658,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -45355,7 +45355,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -46048,7 +46048,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -48135,7 +48135,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -48832,7 +48832,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -49525,7 +49525,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -50919,7 +50919,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -52309,7 +52309,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -53002,7 +53002,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -54396,7 +54396,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -55089,7 +55089,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -55786,7 +55786,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -56479,7 +56479,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -57873,7 +57873,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -58566,7 +58566,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -59263,7 +59263,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -59956,7 +59956,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -61350,7 +61350,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -62043,7 +62043,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -62740,7 +62740,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -63433,7 +63433,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -64827,7 +64827,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -65520,7 +65520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -66217,7 +66217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -66910,7 +66910,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -68304,7 +68304,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -68997,7 +68997,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -69694,7 +69694,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -70387,7 +70387,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -71781,7 +71781,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -72474,7 +72474,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -73171,7 +73171,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -73864,7 +73864,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -75258,7 +75258,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -75951,7 +75951,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -76652,7 +76652,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -77345,7 +77345,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -78739,7 +78739,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -80133,7 +80133,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -80826,7 +80826,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -82220,7 +82220,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -82913,7 +82913,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -83614,7 +83614,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -84307,7 +84307,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -85701,7 +85701,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -86394,7 +86394,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -87095,7 +87095,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -87788,7 +87788,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H126" t="n">
